--- a/output/第10期計画_見える化_将来推計の設定資料の受領点検.xlsx
+++ b/output/第10期計画_見える化_将来推計の設定資料の受領点検.xlsx
@@ -3347,7 +3347,7 @@
     <row r="46" ht="28" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>注6）**見える化システムは令和32年度（2050年度）まで推計します。**中長期の年度はR12・R17・R22・R27・R32の5か年です。
+          <t>注6）見える化システムは令和32年度（2050年度）まで推計します。中長期の年度はR12・R17・R22・R27・R32の5か年です。
 注7）当方は確認事項No.114で「令和22年度までの中長期推計」をお諮りしていましたが、システムは令和32年度まで持っています。算定の範囲を令和32年度まで広げられます。</t>
         </is>
       </c>

--- a/output/第10期計画_見える化_将来推計の設定資料の受領点検.xlsx
+++ b/output/第10期計画_見える化_将来推計の設定資料の受領点検.xlsx
@@ -5172,7 +5172,7 @@
       <c r="D5" s="5" t="inlineStr">
         <is>
           <t>将来推計 第2段階・第3段階
-サービス見込量 第1次概算</t>
+サービス見込量の算定</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -5238,7 +5238,7 @@
       <c r="D7" s="5" t="inlineStr">
         <is>
           <t>将来推計 第2段階
-サービス見込量 第1次概算</t>
+サービス見込量の算定</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -5271,7 +5271,7 @@
       <c r="D8" s="5" t="inlineStr">
         <is>
           <t>将来推計 第2段階
-サービス見込量 第1次概算</t>
+サービス見込量の算定</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -5369,7 +5369,7 @@
       <c r="D11" s="5" t="inlineStr">
         <is>
           <t>将来推計 第2段階
-サービス見込量 第1次概算</t>
+サービス見込量の算定</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
